--- a/output/pdf_financials_xlsx/NATO.xlsx
+++ b/output/pdf_financials_xlsx/NATO.xlsx
@@ -2229,16 +2229,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.576447</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.653486</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.839785</v>
       </c>
     </row>
     <row r="93">
@@ -3596,7 +3596,11 @@
           <t>Reserves (Note 4)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="n">
         <v>0.008800000000000001</v>
       </c>

--- a/output/pdf_financials_xlsx/NATO.xlsx
+++ b/output/pdf_financials_xlsx/NATO.xlsx
@@ -645,7 +645,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001625</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
         <v>-0.999225</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.404697</v>
+        <v>-0.406322</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-0.404697</v>
@@ -988,7 +988,7 @@
         <v>-0.999225</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.398402</v>
+        <v>-0.400027</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.396103</v>
@@ -1081,16 +1081,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.6588580000000001</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.543668</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.077042</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.03672</v>
       </c>
     </row>
     <row r="35">
@@ -1119,16 +1119,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.6588580000000001</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.543668</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.077042</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.03672</v>
       </c>
     </row>
     <row r="37">
@@ -1347,16 +1347,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.660108</v>
+        <v>0.00125</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.567383</v>
+        <v>0.023715</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.100784</v>
+        <v>0.023742</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.056305</v>
+        <v>0.019585</v>
       </c>
     </row>
     <row r="49">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">

--- a/output/pdf_financials_xlsx/NATO.xlsx
+++ b/output/pdf_financials_xlsx/NATO.xlsx
@@ -544,16 +544,16 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.047644</v>
+        <v>0.06514399999999999</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.040018</v>
+        <v>0.306636</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.046555</v>
+        <v>0.201576</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.038279</v>
+        <v>0.164331</v>
       </c>
     </row>
     <row r="8">
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.013733</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.029235</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>-0.149098</v>
@@ -2491,10 +2491,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.110066</v>
+        <v>0.123799</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.09232899999999999</v>
+        <v>0.063094</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>-0.122427</v>
@@ -2592,7 +2592,7 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.024552</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.024552</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -3056,7 +3056,7 @@
         <v>-0.655095</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.594517</v>
+        <v>-0.619069</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-0.160839</v>
@@ -4478,7 +4478,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -4614,7 +4618,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E44" s="5" t="n">
         <v>0.807955</v>
       </c>
@@ -5100,7 +5108,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E58" s="5" t="n">
         <v>0.013733</v>
       </c>
@@ -5408,7 +5420,11 @@
           <t>Consulting and directors’ fees (Note 5)</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -6846,7 +6862,11 @@
           <t>Directors’ fees (Note 5)</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E108" s="5" t="n">
         <v>0.0175</v>
       </c>
